--- a/data/records/初始试模清单.xlsx
+++ b/data/records/初始试模清单.xlsx
@@ -480,31 +480,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B2" t="n">
-        <v>740</v>
+        <v>980</v>
       </c>
       <c r="C2" t="n">
-        <v>360</v>
+        <v>500</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E2" t="n">
         <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J2" t="n">
         <v>16</v>
@@ -520,22 +520,22 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B3" t="n">
-        <v>1020</v>
+        <v>740</v>
       </c>
       <c r="C3" t="n">
-        <v>520</v>
+        <v>280</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -544,7 +544,7 @@
         <v>35</v>
       </c>
       <c r="I3" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
         <v>16</v>
@@ -560,31 +560,31 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B4" t="n">
-        <v>840</v>
+        <v>1180</v>
       </c>
       <c r="C4" t="n">
-        <v>320</v>
+        <v>540</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>15</v>
       </c>
       <c r="F4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G4" t="n">
         <v>35</v>
       </c>
-      <c r="G4" t="n">
-        <v>30</v>
-      </c>
       <c r="H4" t="n">
         <v>25</v>
       </c>
       <c r="I4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
         <v>16</v>
@@ -600,31 +600,31 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B5" t="n">
-        <v>1180</v>
+        <v>940</v>
       </c>
       <c r="C5" t="n">
-        <v>520</v>
+        <v>420</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="J5" t="n">
         <v>16</v>
@@ -640,31 +640,31 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B6" t="n">
-        <v>920</v>
+        <v>1080</v>
       </c>
       <c r="C6" t="n">
-        <v>600</v>
+        <v>320</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="n">
         <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H6" t="n">
         <v>30</v>
       </c>
       <c r="I6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
         <v>16</v>
@@ -683,28 +683,28 @@
         <v>138</v>
       </c>
       <c r="B7" t="n">
-        <v>1120</v>
+        <v>820</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E7" t="n">
         <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
         <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J7" t="n">
         <v>16</v>
@@ -720,31 +720,31 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B8" t="n">
-        <v>820</v>
+        <v>1040</v>
       </c>
       <c r="C8" t="n">
-        <v>440</v>
+        <v>360</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G8" t="n">
+        <v>25</v>
+      </c>
+      <c r="H8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I8" t="n">
         <v>40</v>
-      </c>
-      <c r="G8" t="n">
-        <v>35</v>
-      </c>
-      <c r="H8" t="n">
-        <v>10</v>
-      </c>
-      <c r="I8" t="n">
-        <v>20</v>
       </c>
       <c r="J8" t="n">
         <v>16</v>
@@ -760,22 +760,22 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B9" t="n">
-        <v>980</v>
+        <v>780</v>
       </c>
       <c r="C9" t="n">
-        <v>280</v>
+        <v>580</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>30</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
         <v>15</v>
@@ -784,7 +784,7 @@
         <v>35</v>
       </c>
       <c r="I9" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
         <v>16</v>
@@ -800,31 +800,31 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B10" t="n">
-        <v>860</v>
+        <v>1160</v>
       </c>
       <c r="C10" t="n">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E10" t="n">
+        <v>15</v>
+      </c>
+      <c r="F10" t="n">
         <v>5</v>
       </c>
-      <c r="F10" t="n">
-        <v>20</v>
-      </c>
       <c r="G10" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
         <v>30</v>
       </c>
       <c r="I10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
         <v>16</v>
@@ -840,31 +840,31 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B11" t="n">
-        <v>1140</v>
+        <v>920</v>
       </c>
       <c r="C11" t="n">
-        <v>260</v>
+        <v>600</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J11" t="n">
         <v>16</v>
@@ -880,31 +880,31 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B12" t="n">
-        <v>700</v>
+        <v>960</v>
       </c>
       <c r="C12" t="n">
-        <v>560</v>
+        <v>320</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F12" t="n">
         <v>30</v>
       </c>
       <c r="G12" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J12" t="n">
         <v>16</v>
@@ -920,22 +920,22 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B13" t="n">
-        <v>1060</v>
+        <v>700</v>
       </c>
       <c r="C13" t="n">
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G13" t="n">
         <v>15</v>
@@ -944,7 +944,7 @@
         <v>40</v>
       </c>
       <c r="I13" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J13" t="n">
         <v>16</v>
@@ -960,31 +960,31 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B14" t="n">
-        <v>780</v>
+        <v>1080</v>
       </c>
       <c r="C14" t="n">
-        <v>320</v>
+        <v>520</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E14" t="n">
         <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I14" t="n">
         <v>35</v>
-      </c>
-      <c r="H14" t="n">
-        <v>5</v>
-      </c>
-      <c r="I14" t="n">
-        <v>20</v>
       </c>
       <c r="J14" t="n">
         <v>16</v>
@@ -1000,31 +1000,31 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B15" t="n">
-        <v>1020</v>
+        <v>820</v>
       </c>
       <c r="C15" t="n">
-        <v>480</v>
+        <v>380</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E15" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F15" t="n">
+        <v>30</v>
+      </c>
+      <c r="G15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H15" t="n">
         <v>35</v>
       </c>
-      <c r="G15" t="n">
-        <v>20</v>
-      </c>
-      <c r="H15" t="n">
-        <v>30</v>
-      </c>
       <c r="I15" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="J15" t="n">
         <v>16</v>
@@ -1040,31 +1040,31 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B16" t="n">
-        <v>940</v>
+        <v>1120</v>
       </c>
       <c r="C16" t="n">
-        <v>340</v>
+        <v>480</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>35</v>
       </c>
       <c r="F16" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G16" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H16" t="n">
         <v>25</v>
       </c>
       <c r="I16" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J16" t="n">
         <v>16</v>
@@ -1080,31 +1080,31 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B17" t="n">
-        <v>1100</v>
+        <v>860</v>
       </c>
       <c r="C17" t="n">
-        <v>540</v>
+        <v>260</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="J17" t="n">
         <v>16</v>
@@ -1120,23 +1120,23 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B18" t="n">
-        <v>920</v>
+        <v>1120</v>
       </c>
       <c r="C18" t="n">
-        <v>260</v>
+        <v>580</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
+        <v>25</v>
+      </c>
+      <c r="F18" t="n">
         <v>30</v>
       </c>
-      <c r="F18" t="n">
-        <v>35</v>
-      </c>
       <c r="G18" t="n">
         <v>20</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>25</v>
       </c>
       <c r="I18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
         <v>16</v>
@@ -1160,31 +1160,31 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B19" t="n">
-        <v>1080</v>
+        <v>880</v>
       </c>
       <c r="C19" t="n">
-        <v>460</v>
+        <v>360</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
         <v>16</v>
@@ -1200,31 +1200,31 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B20" t="n">
-        <v>780</v>
+        <v>1040</v>
       </c>
       <c r="C20" t="n">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G20" t="n">
         <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I20" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="J20" t="n">
         <v>16</v>
@@ -1240,31 +1240,31 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B21" t="n">
-        <v>980</v>
+        <v>800</v>
       </c>
       <c r="C21" t="n">
-        <v>560</v>
+        <v>320</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E21" t="n">
         <v>40</v>
       </c>
       <c r="F21" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H21" t="n">
         <v>35</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J21" t="n">
         <v>16</v>

--- a/data/records/初始试模清单.xlsx
+++ b/data/records/初始试模清单.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,31 +480,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B2" t="n">
-        <v>980</v>
+        <v>760</v>
       </c>
       <c r="C2" t="n">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F2" t="n">
         <v>40</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H2" t="n">
         <v>15</v>
       </c>
-      <c r="G2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>20</v>
-      </c>
-      <c r="I2" t="n">
-        <v>30</v>
       </c>
       <c r="J2" t="n">
         <v>16</v>
@@ -520,31 +520,31 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B3" t="n">
-        <v>740</v>
+        <v>1160</v>
       </c>
       <c r="C3" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" t="n">
-        <v>35</v>
-      </c>
-      <c r="G3" t="n">
-        <v>20</v>
-      </c>
       <c r="H3" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J3" t="n">
         <v>16</v>
@@ -560,31 +560,31 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B4" t="n">
-        <v>1180</v>
+        <v>900</v>
       </c>
       <c r="C4" t="n">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>25</v>
       </c>
-      <c r="G4" t="n">
-        <v>35</v>
-      </c>
       <c r="H4" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J4" t="n">
         <v>16</v>
@@ -600,31 +600,31 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B5" t="n">
-        <v>940</v>
+        <v>1040</v>
       </c>
       <c r="C5" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
         <v>25</v>
       </c>
       <c r="F5" t="n">
+        <v>25</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="n">
         <v>5</v>
       </c>
-      <c r="G5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H5" t="n">
-        <v>10</v>
-      </c>
       <c r="I5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
         <v>16</v>
@@ -640,31 +640,31 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B6" t="n">
-        <v>1080</v>
+        <v>840</v>
       </c>
       <c r="C6" t="n">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" t="n">
+        <v>35</v>
+      </c>
+      <c r="G6" t="n">
         <v>25</v>
       </c>
-      <c r="F6" t="n">
-        <v>20</v>
-      </c>
-      <c r="G6" t="n">
-        <v>35</v>
-      </c>
       <c r="H6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J6" t="n">
         <v>16</v>
@@ -680,31 +680,31 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B7" t="n">
-        <v>820</v>
+        <v>980</v>
       </c>
       <c r="C7" t="n">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" t="n">
         <v>10</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>25</v>
       </c>
       <c r="J7" t="n">
         <v>16</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B8" t="n">
-        <v>1040</v>
+        <v>720</v>
       </c>
       <c r="C8" t="n">
         <v>360</v>
@@ -732,19 +732,19 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H8" t="n">
         <v>20</v>
       </c>
       <c r="I8" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="J8" t="n">
         <v>16</v>
@@ -760,31 +760,31 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B9" t="n">
-        <v>780</v>
+        <v>1100</v>
       </c>
       <c r="C9" t="n">
-        <v>580</v>
+        <v>520</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E9" t="n">
+        <v>35</v>
+      </c>
+      <c r="F9" t="n">
         <v>30</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>10</v>
       </c>
-      <c r="G9" t="n">
-        <v>15</v>
-      </c>
       <c r="H9" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="J9" t="n">
         <v>16</v>
@@ -800,31 +800,31 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B10" t="n">
-        <v>1160</v>
+        <v>920</v>
       </c>
       <c r="C10" t="n">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E10" t="n">
         <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J10" t="n">
         <v>16</v>
@@ -840,31 +840,31 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B11" t="n">
-        <v>920</v>
+        <v>1080</v>
       </c>
       <c r="C11" t="n">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H11" t="n">
         <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
         <v>16</v>
@@ -873,406 +873,6 @@
         <v>8</v>
       </c>
       <c r="L11" t="inlineStr">
-        <is>
-          <t>[2, 1, 0.5, 0.5]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>139</v>
-      </c>
-      <c r="B12" t="n">
-        <v>960</v>
-      </c>
-      <c r="C12" t="n">
-        <v>320</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>25</v>
-      </c>
-      <c r="F12" t="n">
-        <v>30</v>
-      </c>
-      <c r="G12" t="n">
-        <v>25</v>
-      </c>
-      <c r="H12" t="n">
-        <v>15</v>
-      </c>
-      <c r="I12" t="n">
-        <v>35</v>
-      </c>
-      <c r="J12" t="n">
-        <v>16</v>
-      </c>
-      <c r="K12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>[2, 1, 0.5, 0.5]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>143</v>
-      </c>
-      <c r="B13" t="n">
-        <v>700</v>
-      </c>
-      <c r="C13" t="n">
-        <v>460</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>20</v>
-      </c>
-      <c r="F13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G13" t="n">
-        <v>15</v>
-      </c>
-      <c r="H13" t="n">
-        <v>40</v>
-      </c>
-      <c r="I13" t="n">
-        <v>10</v>
-      </c>
-      <c r="J13" t="n">
-        <v>16</v>
-      </c>
-      <c r="K13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>[2, 1, 0.5, 0.5]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>141</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1080</v>
-      </c>
-      <c r="C14" t="n">
-        <v>520</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E14" t="n">
-        <v>20</v>
-      </c>
-      <c r="F14" t="n">
-        <v>15</v>
-      </c>
-      <c r="G14" t="n">
-        <v>30</v>
-      </c>
-      <c r="H14" t="n">
-        <v>20</v>
-      </c>
-      <c r="I14" t="n">
-        <v>35</v>
-      </c>
-      <c r="J14" t="n">
-        <v>16</v>
-      </c>
-      <c r="K14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>[2, 1, 0.5, 0.5]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>139</v>
-      </c>
-      <c r="B15" t="n">
-        <v>820</v>
-      </c>
-      <c r="C15" t="n">
-        <v>380</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>30</v>
-      </c>
-      <c r="F15" t="n">
-        <v>30</v>
-      </c>
-      <c r="G15" t="n">
-        <v>20</v>
-      </c>
-      <c r="H15" t="n">
-        <v>35</v>
-      </c>
-      <c r="I15" t="n">
-        <v>10</v>
-      </c>
-      <c r="J15" t="n">
-        <v>16</v>
-      </c>
-      <c r="K15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>[2, 1, 0.5, 0.5]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>137</v>
-      </c>
-      <c r="B16" t="n">
-        <v>1120</v>
-      </c>
-      <c r="C16" t="n">
-        <v>480</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>35</v>
-      </c>
-      <c r="F16" t="n">
-        <v>35</v>
-      </c>
-      <c r="G16" t="n">
-        <v>40</v>
-      </c>
-      <c r="H16" t="n">
-        <v>25</v>
-      </c>
-      <c r="I16" t="n">
-        <v>15</v>
-      </c>
-      <c r="J16" t="n">
-        <v>16</v>
-      </c>
-      <c r="K16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>[2, 1, 0.5, 0.5]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>140</v>
-      </c>
-      <c r="B17" t="n">
-        <v>860</v>
-      </c>
-      <c r="C17" t="n">
-        <v>260</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" t="n">
-        <v>5</v>
-      </c>
-      <c r="F17" t="n">
-        <v>20</v>
-      </c>
-      <c r="G17" t="n">
-        <v>15</v>
-      </c>
-      <c r="H17" t="n">
-        <v>10</v>
-      </c>
-      <c r="I17" t="n">
-        <v>30</v>
-      </c>
-      <c r="J17" t="n">
-        <v>16</v>
-      </c>
-      <c r="K17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>[2, 1, 0.5, 0.5]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>140</v>
-      </c>
-      <c r="B18" t="n">
-        <v>1120</v>
-      </c>
-      <c r="C18" t="n">
-        <v>580</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>25</v>
-      </c>
-      <c r="F18" t="n">
-        <v>30</v>
-      </c>
-      <c r="G18" t="n">
-        <v>20</v>
-      </c>
-      <c r="H18" t="n">
-        <v>25</v>
-      </c>
-      <c r="I18" t="n">
-        <v>25</v>
-      </c>
-      <c r="J18" t="n">
-        <v>16</v>
-      </c>
-      <c r="K18" t="n">
-        <v>8</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>[2, 1, 0.5, 0.5]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>137</v>
-      </c>
-      <c r="B19" t="n">
-        <v>880</v>
-      </c>
-      <c r="C19" t="n">
-        <v>360</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>15</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>25</v>
-      </c>
-      <c r="H19" t="n">
-        <v>15</v>
-      </c>
-      <c r="I19" t="n">
-        <v>20</v>
-      </c>
-      <c r="J19" t="n">
-        <v>16</v>
-      </c>
-      <c r="K19" t="n">
-        <v>8</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>[2, 1, 0.5, 0.5]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>139</v>
-      </c>
-      <c r="B20" t="n">
-        <v>1040</v>
-      </c>
-      <c r="C20" t="n">
-        <v>460</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E20" t="n">
-        <v>10</v>
-      </c>
-      <c r="F20" t="n">
-        <v>20</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10</v>
-      </c>
-      <c r="H20" t="n">
-        <v>20</v>
-      </c>
-      <c r="I20" t="n">
-        <v>10</v>
-      </c>
-      <c r="J20" t="n">
-        <v>16</v>
-      </c>
-      <c r="K20" t="n">
-        <v>8</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>[2, 1, 0.5, 0.5]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>141</v>
-      </c>
-      <c r="B21" t="n">
-        <v>800</v>
-      </c>
-      <c r="C21" t="n">
-        <v>320</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E21" t="n">
-        <v>40</v>
-      </c>
-      <c r="F21" t="n">
-        <v>35</v>
-      </c>
-      <c r="G21" t="n">
-        <v>40</v>
-      </c>
-      <c r="H21" t="n">
-        <v>35</v>
-      </c>
-      <c r="I21" t="n">
-        <v>35</v>
-      </c>
-      <c r="J21" t="n">
-        <v>16</v>
-      </c>
-      <c r="K21" t="n">
-        <v>8</v>
-      </c>
-      <c r="L21" t="inlineStr">
         <is>
           <t>[2, 1, 0.5, 0.5]</t>
         </is>

--- a/data/records/初始试模清单.xlsx
+++ b/data/records/初始试模清单.xlsx
@@ -483,28 +483,28 @@
         <v>138</v>
       </c>
       <c r="B2" t="n">
-        <v>760</v>
+        <v>960</v>
       </c>
       <c r="C2" t="n">
-        <v>520</v>
+        <v>260</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>40</v>
       </c>
-      <c r="G2" t="n">
-        <v>35</v>
-      </c>
       <c r="H2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I2" t="n">
         <v>15</v>
-      </c>
-      <c r="I2" t="n">
-        <v>20</v>
       </c>
       <c r="J2" t="n">
         <v>16</v>
@@ -520,13 +520,13 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B3" t="n">
-        <v>1160</v>
+        <v>760</v>
       </c>
       <c r="C3" t="n">
-        <v>320</v>
+        <v>560</v>
       </c>
       <c r="D3" t="n">
         <v>1.5</v>
@@ -535,16 +535,16 @@
         <v>20</v>
       </c>
       <c r="F3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G3" t="n">
         <v>20</v>
-      </c>
-      <c r="G3" t="n">
-        <v>10</v>
       </c>
       <c r="H3" t="n">
         <v>25</v>
       </c>
       <c r="I3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J3" t="n">
         <v>16</v>
@@ -560,28 +560,28 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B4" t="n">
-        <v>900</v>
+        <v>1120</v>
       </c>
       <c r="C4" t="n">
-        <v>600</v>
+        <v>360</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
         <v>25</v>
       </c>
       <c r="H4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I4" t="n">
         <v>35</v>
@@ -603,28 +603,28 @@
         <v>137</v>
       </c>
       <c r="B5" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="C5" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
         <v>5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>15</v>
       </c>
       <c r="J5" t="n">
         <v>16</v>
@@ -643,25 +643,25 @@
         <v>136</v>
       </c>
       <c r="B6" t="n">
-        <v>840</v>
+        <v>1180</v>
       </c>
       <c r="C6" t="n">
-        <v>280</v>
+        <v>560</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>30</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>35</v>
-      </c>
-      <c r="G6" t="n">
-        <v>25</v>
-      </c>
-      <c r="H6" t="n">
-        <v>40</v>
       </c>
       <c r="I6" t="n">
         <v>35</v>
@@ -680,13 +680,13 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B7" t="n">
-        <v>980</v>
+        <v>860</v>
       </c>
       <c r="C7" t="n">
-        <v>420</v>
+        <v>320</v>
       </c>
       <c r="D7" t="n">
         <v>0.5</v>
@@ -695,7 +695,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
         <v>15</v>
@@ -704,7 +704,7 @@
         <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
         <v>16</v>
@@ -720,13 +720,13 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B8" t="n">
-        <v>720</v>
+        <v>1040</v>
       </c>
       <c r="C8" t="n">
-        <v>360</v>
+        <v>440</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -735,16 +735,16 @@
         <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
         <v>35</v>
       </c>
       <c r="H8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" t="n">
         <v>20</v>
-      </c>
-      <c r="I8" t="n">
-        <v>15</v>
       </c>
       <c r="J8" t="n">
         <v>16</v>
@@ -763,28 +763,28 @@
         <v>139</v>
       </c>
       <c r="B9" t="n">
-        <v>1100</v>
+        <v>720</v>
       </c>
       <c r="C9" t="n">
-        <v>520</v>
+        <v>380</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F9" t="n">
+        <v>15</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" t="n">
         <v>30</v>
       </c>
-      <c r="G9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H9" t="n">
-        <v>25</v>
-      </c>
       <c r="I9" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J9" t="n">
         <v>16</v>
@@ -803,10 +803,10 @@
         <v>139</v>
       </c>
       <c r="B10" t="n">
-        <v>920</v>
+        <v>1100</v>
       </c>
       <c r="C10" t="n">
-        <v>360</v>
+        <v>460</v>
       </c>
       <c r="D10" t="n">
         <v>0.5</v>
@@ -815,16 +815,16 @@
         <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G10" t="n">
         <v>25</v>
       </c>
       <c r="H10" t="n">
+        <v>35</v>
+      </c>
+      <c r="I10" t="n">
         <v>40</v>
-      </c>
-      <c r="I10" t="n">
-        <v>35</v>
       </c>
       <c r="J10" t="n">
         <v>16</v>
@@ -843,25 +843,25 @@
         <v>141</v>
       </c>
       <c r="B11" t="n">
-        <v>1080</v>
+        <v>920</v>
       </c>
       <c r="C11" t="n">
-        <v>560</v>
+        <v>420</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="G11" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" t="n">
         <v>15</v>
-      </c>
-      <c r="H11" t="n">
-        <v>10</v>
       </c>
       <c r="I11" t="n">
         <v>10</v>

--- a/data/records/初始试模清单.xlsx
+++ b/data/records/初始试模清单.xlsx
@@ -480,31 +480,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B2" t="n">
-        <v>960</v>
+        <v>700</v>
       </c>
       <c r="C2" t="n">
-        <v>260</v>
+        <v>380</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G2" t="n">
         <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40</v>
       </c>
       <c r="H2" t="n">
         <v>20</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J2" t="n">
         <v>16</v>
@@ -520,31 +520,31 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B3" t="n">
-        <v>760</v>
+        <v>1000</v>
       </c>
       <c r="C3" t="n">
-        <v>560</v>
+        <v>520</v>
       </c>
       <c r="D3" t="n">
         <v>1.5</v>
       </c>
       <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
         <v>20</v>
       </c>
-      <c r="F3" t="n">
-        <v>35</v>
-      </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H3" t="n">
         <v>25</v>
       </c>
       <c r="I3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
         <v>16</v>
@@ -560,31 +560,31 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B4" t="n">
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="C4" t="n">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="F4" t="n">
-        <v>25</v>
-      </c>
       <c r="G4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I4" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
         <v>16</v>
@@ -600,31 +600,31 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B5" t="n">
-        <v>940</v>
+        <v>1140</v>
       </c>
       <c r="C5" t="n">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F5" t="n">
+        <v>25</v>
+      </c>
+      <c r="G5" t="n">
         <v>35</v>
       </c>
-      <c r="F5" t="n">
-        <v>20</v>
-      </c>
-      <c r="G5" t="n">
-        <v>10</v>
-      </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="J5" t="n">
         <v>16</v>
@@ -640,31 +640,31 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B6" t="n">
-        <v>1180</v>
+        <v>880</v>
       </c>
       <c r="C6" t="n">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="D6" t="n">
         <v>1.5</v>
       </c>
       <c r="E6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" t="n">
         <v>35</v>
       </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H6" t="n">
         <v>35</v>
       </c>
       <c r="I6" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
         <v>16</v>
@@ -680,31 +680,31 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B7" t="n">
-        <v>860</v>
+        <v>1200</v>
       </c>
       <c r="C7" t="n">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J7" t="n">
         <v>16</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B8" t="n">
-        <v>1040</v>
+        <v>760</v>
       </c>
       <c r="C8" t="n">
         <v>440</v>
@@ -732,19 +732,19 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
         <v>15</v>
       </c>
       <c r="I8" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J8" t="n">
         <v>16</v>
@@ -760,31 +760,31 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B9" t="n">
-        <v>720</v>
+        <v>1080</v>
       </c>
       <c r="C9" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E9" t="n">
+        <v>40</v>
+      </c>
+      <c r="F9" t="n">
+        <v>30</v>
+      </c>
+      <c r="G9" t="n">
         <v>25</v>
-      </c>
-      <c r="F9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G9" t="n">
-        <v>15</v>
       </c>
       <c r="H9" t="n">
         <v>30</v>
       </c>
       <c r="I9" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J9" t="n">
         <v>16</v>
@@ -800,31 +800,31 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B10" t="n">
-        <v>1100</v>
+        <v>860</v>
       </c>
       <c r="C10" t="n">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>25</v>
+      </c>
+      <c r="G10" t="n">
         <v>15</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
+        <v>40</v>
+      </c>
+      <c r="I10" t="n">
         <v>20</v>
-      </c>
-      <c r="G10" t="n">
-        <v>25</v>
-      </c>
-      <c r="H10" t="n">
-        <v>35</v>
-      </c>
-      <c r="I10" t="n">
-        <v>40</v>
       </c>
       <c r="J10" t="n">
         <v>16</v>
@@ -840,13 +840,13 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B11" t="n">
-        <v>920</v>
+        <v>1100</v>
       </c>
       <c r="C11" t="n">
-        <v>420</v>
+        <v>280</v>
       </c>
       <c r="D11" t="n">
         <v>1.5</v>
@@ -855,16 +855,16 @@
         <v>30</v>
       </c>
       <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
+        <v>35</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n">
         <v>30</v>
-      </c>
-      <c r="G11" t="n">
-        <v>10</v>
-      </c>
-      <c r="H11" t="n">
-        <v>15</v>
-      </c>
-      <c r="I11" t="n">
-        <v>10</v>
       </c>
       <c r="J11" t="n">
         <v>16</v>

--- a/data/records/初始试模清单.xlsx
+++ b/data/records/初始试模清单.xlsx
@@ -480,31 +480,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B2" t="n">
-        <v>700</v>
+        <v>860</v>
       </c>
       <c r="C2" t="n">
-        <v>380</v>
+        <v>460</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" t="n">
         <v>35</v>
       </c>
-      <c r="F2" t="n">
-        <v>40</v>
-      </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H2" t="n">
         <v>20</v>
       </c>
       <c r="I2" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
         <v>16</v>
@@ -520,31 +520,31 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B3" t="n">
-        <v>1000</v>
+        <v>1060</v>
       </c>
       <c r="C3" t="n">
-        <v>520</v>
+        <v>360</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="J3" t="n">
         <v>16</v>
@@ -560,31 +560,31 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B4" t="n">
-        <v>840</v>
+        <v>760</v>
       </c>
       <c r="C4" t="n">
-        <v>340</v>
+        <v>600</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J4" t="n">
         <v>16</v>
@@ -600,31 +600,31 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B5" t="n">
-        <v>1140</v>
+        <v>1080</v>
       </c>
       <c r="C5" t="n">
-        <v>480</v>
+        <v>320</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
         <v>25</v>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
         <v>16</v>
@@ -640,31 +640,31 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B6" t="n">
-        <v>880</v>
+        <v>760</v>
       </c>
       <c r="C6" t="n">
-        <v>580</v>
+        <v>420</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
         <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H6" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J6" t="n">
         <v>16</v>
@@ -680,31 +680,31 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B7" t="n">
         <v>1200</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
         <v>16</v>
@@ -720,31 +720,31 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B8" t="n">
-        <v>760</v>
+        <v>900</v>
       </c>
       <c r="C8" t="n">
-        <v>440</v>
+        <v>280</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E8" t="n">
+        <v>35</v>
+      </c>
+      <c r="F8" t="n">
         <v>15</v>
       </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I8" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
         <v>16</v>
@@ -760,31 +760,31 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B9" t="n">
-        <v>1080</v>
+        <v>960</v>
       </c>
       <c r="C9" t="n">
-        <v>260</v>
+        <v>540</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
         <v>30</v>
       </c>
       <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="n">
         <v>25</v>
       </c>
-      <c r="H9" t="n">
-        <v>30</v>
-      </c>
       <c r="I9" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J9" t="n">
         <v>16</v>
@@ -800,31 +800,31 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B10" t="n">
-        <v>860</v>
+        <v>820</v>
       </c>
       <c r="C10" t="n">
-        <v>440</v>
+        <v>260</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
         <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J10" t="n">
         <v>16</v>
@@ -840,31 +840,31 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B11" t="n">
-        <v>1100</v>
+        <v>1120</v>
       </c>
       <c r="C11" t="n">
-        <v>280</v>
+        <v>540</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
         <v>16</v>

--- a/data/records/初始试模清单.xlsx
+++ b/data/records/初始试模清单.xlsx
@@ -480,31 +480,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B2" t="n">
-        <v>860</v>
+        <v>1120</v>
       </c>
       <c r="C2" t="n">
-        <v>460</v>
+        <v>340</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="J2" t="n">
         <v>16</v>
@@ -520,31 +520,31 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B3" t="n">
-        <v>1060</v>
+        <v>760</v>
       </c>
       <c r="C3" t="n">
-        <v>360</v>
+        <v>560</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H3" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
         <v>16</v>
@@ -560,31 +560,31 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B4" t="n">
-        <v>760</v>
+        <v>960</v>
       </c>
       <c r="C4" t="n">
-        <v>600</v>
+        <v>280</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G4" t="n">
+        <v>35</v>
+      </c>
+      <c r="H4" t="n">
         <v>20</v>
       </c>
-      <c r="G4" t="n">
-        <v>40</v>
-      </c>
-      <c r="H4" t="n">
-        <v>40</v>
-      </c>
       <c r="I4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
         <v>16</v>
@@ -600,31 +600,31 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B5" t="n">
-        <v>1080</v>
+        <v>840</v>
       </c>
       <c r="C5" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="D5" t="n">
         <v>1.5</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" t="n">
         <v>25</v>
-      </c>
-      <c r="G5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H5" t="n">
-        <v>10</v>
-      </c>
-      <c r="I5" t="n">
-        <v>20</v>
       </c>
       <c r="J5" t="n">
         <v>16</v>
@@ -640,31 +640,31 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B6" t="n">
-        <v>760</v>
+        <v>1040</v>
       </c>
       <c r="C6" t="n">
-        <v>420</v>
+        <v>520</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" t="n">
         <v>10</v>
       </c>
-      <c r="F6" t="n">
-        <v>35</v>
-      </c>
       <c r="G6" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
         <v>16</v>
@@ -680,31 +680,31 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B7" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="C7" t="n">
-        <v>500</v>
+        <v>380</v>
       </c>
       <c r="D7" t="n">
         <v>0.5</v>
       </c>
       <c r="E7" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" t="n">
         <v>25</v>
       </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J7" t="n">
         <v>16</v>
@@ -720,31 +720,31 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B8" t="n">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="C8" t="n">
-        <v>280</v>
+        <v>440</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
+        <v>30</v>
+      </c>
+      <c r="F8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G8" t="n">
+        <v>25</v>
+      </c>
+      <c r="H8" t="n">
         <v>35</v>
       </c>
-      <c r="F8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G8" t="n">
-        <v>30</v>
-      </c>
-      <c r="H8" t="n">
-        <v>20</v>
-      </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="J8" t="n">
         <v>16</v>
@@ -760,31 +760,31 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B9" t="n">
-        <v>960</v>
+        <v>800</v>
       </c>
       <c r="C9" t="n">
-        <v>540</v>
+        <v>320</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
         <v>20</v>
       </c>
-      <c r="F9" t="n">
-        <v>30</v>
-      </c>
       <c r="G9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="J9" t="n">
         <v>16</v>
@@ -800,31 +800,31 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B10" t="n">
-        <v>820</v>
+        <v>1000</v>
       </c>
       <c r="C10" t="n">
-        <v>260</v>
+        <v>440</v>
       </c>
       <c r="D10" t="n">
         <v>0.5</v>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G10" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H10" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
         <v>16</v>
@@ -840,31 +840,31 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B11" t="n">
-        <v>1120</v>
+        <v>860</v>
       </c>
       <c r="C11" t="n">
-        <v>540</v>
+        <v>320</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J11" t="n">
         <v>16</v>

--- a/data/records/初始试模清单.xlsx
+++ b/data/records/初始试模清单.xlsx
@@ -480,13 +480,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B2" t="n">
-        <v>1120</v>
+        <v>960</v>
       </c>
       <c r="C2" t="n">
-        <v>340</v>
+        <v>540</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H2" t="n">
         <v>25</v>
-      </c>
-      <c r="H2" t="n">
-        <v>30</v>
       </c>
       <c r="I2" t="n">
         <v>35</v>
@@ -523,28 +523,28 @@
         <v>138</v>
       </c>
       <c r="B3" t="n">
-        <v>760</v>
+        <v>920</v>
       </c>
       <c r="C3" t="n">
-        <v>560</v>
+        <v>420</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" t="n">
         <v>5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>20</v>
       </c>
       <c r="J3" t="n">
         <v>16</v>
@@ -560,31 +560,31 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B4" t="n">
-        <v>960</v>
+        <v>1120</v>
       </c>
       <c r="C4" t="n">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H4" t="n">
         <v>20</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
         <v>16</v>
@@ -600,13 +600,13 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B5" t="n">
-        <v>840</v>
+        <v>780</v>
       </c>
       <c r="C5" t="n">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="D5" t="n">
         <v>1.5</v>
@@ -615,16 +615,16 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G5" t="n">
         <v>15</v>
       </c>
       <c r="H5" t="n">
+        <v>35</v>
+      </c>
+      <c r="I5" t="n">
         <v>30</v>
-      </c>
-      <c r="I5" t="n">
-        <v>25</v>
       </c>
       <c r="J5" t="n">
         <v>16</v>
@@ -640,13 +640,13 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B6" t="n">
-        <v>1040</v>
+        <v>1160</v>
       </c>
       <c r="C6" t="n">
-        <v>520</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -655,16 +655,16 @@
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H6" t="n">
         <v>15</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J6" t="n">
         <v>16</v>
@@ -680,28 +680,28 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B7" t="n">
-        <v>900</v>
+        <v>760</v>
       </c>
       <c r="C7" t="n">
-        <v>380</v>
+        <v>600</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>30</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I7" t="n">
         <v>25</v>
@@ -723,25 +723,25 @@
         <v>139</v>
       </c>
       <c r="B8" t="n">
-        <v>1200</v>
+        <v>1040</v>
       </c>
       <c r="C8" t="n">
-        <v>440</v>
+        <v>320</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E8" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G8" t="n">
+        <v>40</v>
+      </c>
+      <c r="H8" t="n">
         <v>30</v>
-      </c>
-      <c r="F8" t="n">
-        <v>30</v>
-      </c>
-      <c r="G8" t="n">
-        <v>25</v>
-      </c>
-      <c r="H8" t="n">
-        <v>35</v>
       </c>
       <c r="I8" t="n">
         <v>35</v>
@@ -763,25 +763,25 @@
         <v>142</v>
       </c>
       <c r="B9" t="n">
-        <v>800</v>
+        <v>840</v>
       </c>
       <c r="C9" t="n">
-        <v>320</v>
+        <v>440</v>
       </c>
       <c r="D9" t="n">
         <v>0.5</v>
       </c>
       <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>25</v>
+      </c>
+      <c r="G9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" t="n">
         <v>5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>20</v>
-      </c>
-      <c r="G9" t="n">
-        <v>15</v>
-      </c>
-      <c r="H9" t="n">
-        <v>10</v>
       </c>
       <c r="I9" t="n">
         <v>15</v>
@@ -803,28 +803,28 @@
         <v>141</v>
       </c>
       <c r="B10" t="n">
-        <v>1000</v>
+        <v>1080</v>
       </c>
       <c r="C10" t="n">
-        <v>440</v>
+        <v>320</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J10" t="n">
         <v>16</v>
@@ -843,28 +843,28 @@
         <v>139</v>
       </c>
       <c r="B11" t="n">
-        <v>860</v>
+        <v>800</v>
       </c>
       <c r="C11" t="n">
-        <v>320</v>
+        <v>460</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
+        <v>20</v>
+      </c>
+      <c r="G11" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" t="n">
         <v>40</v>
       </c>
-      <c r="G11" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>25</v>
-      </c>
-      <c r="I11" t="n">
-        <v>30</v>
       </c>
       <c r="J11" t="n">
         <v>16</v>

--- a/data/records/初始试模清单.xlsx
+++ b/data/records/初始试模清单.xlsx
@@ -483,28 +483,28 @@
         <v>143</v>
       </c>
       <c r="B2" t="n">
-        <v>960</v>
+        <v>1040</v>
       </c>
       <c r="C2" t="n">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G2" t="n">
         <v>40</v>
       </c>
-      <c r="G2" t="n">
-        <v>35</v>
-      </c>
       <c r="H2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I2" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
         <v>16</v>
@@ -523,7 +523,7 @@
         <v>138</v>
       </c>
       <c r="B3" t="n">
-        <v>920</v>
+        <v>740</v>
       </c>
       <c r="C3" t="n">
         <v>420</v>
@@ -532,19 +532,19 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
         <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="J3" t="n">
         <v>16</v>
@@ -560,31 +560,31 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B4" t="n">
-        <v>1120</v>
+        <v>1100</v>
       </c>
       <c r="C4" t="n">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="D4" t="n">
         <v>0.5</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H4" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J4" t="n">
         <v>16</v>
@@ -600,31 +600,31 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B5" t="n">
-        <v>780</v>
+        <v>920</v>
       </c>
       <c r="C5" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H5" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I5" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
         <v>16</v>
@@ -640,31 +640,31 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B6" t="n">
-        <v>1160</v>
+        <v>1200</v>
       </c>
       <c r="C6" t="n">
         <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G6" t="n">
+        <v>25</v>
+      </c>
+      <c r="H6" t="n">
         <v>35</v>
       </c>
-      <c r="G6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H6" t="n">
-        <v>15</v>
-      </c>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="J6" t="n">
         <v>16</v>
@@ -683,28 +683,28 @@
         <v>137</v>
       </c>
       <c r="B7" t="n">
-        <v>760</v>
+        <v>820</v>
       </c>
       <c r="C7" t="n">
-        <v>600</v>
+        <v>520</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J7" t="n">
         <v>16</v>
@@ -723,28 +723,28 @@
         <v>139</v>
       </c>
       <c r="B8" t="n">
-        <v>1040</v>
+        <v>1000</v>
       </c>
       <c r="C8" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="D8" t="n">
         <v>1.5</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
         <v>20</v>
-      </c>
-      <c r="G8" t="n">
-        <v>40</v>
-      </c>
-      <c r="H8" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" t="n">
-        <v>35</v>
       </c>
       <c r="J8" t="n">
         <v>16</v>
@@ -763,28 +763,28 @@
         <v>142</v>
       </c>
       <c r="B9" t="n">
-        <v>840</v>
+        <v>780</v>
       </c>
       <c r="C9" t="n">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
         <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I9" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J9" t="n">
         <v>16</v>
@@ -803,28 +803,28 @@
         <v>141</v>
       </c>
       <c r="B10" t="n">
-        <v>1080</v>
+        <v>1140</v>
       </c>
       <c r="C10" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
         <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H10" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="I10" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J10" t="n">
         <v>16</v>
@@ -843,28 +843,28 @@
         <v>139</v>
       </c>
       <c r="B11" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="C11" t="n">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H11" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="I11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
         <v>16</v>
